--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -166,7 +166,7 @@
     <t>◇バトル編成について
 ■編成
 バトルに参加するメンバーは最大5名まで編成できます。
-メンバーはそれぞれFront・Backに配置できます。
+メンバーはそれぞれ前列・後列に配置できます。
 Backに配置したメンバーはRangeがLの魔法のみ使用できます。
 ◇バトルシステム
 ■バトル
@@ -203,7 +203,7 @@
 キャラクターはそれぞれキャラ毎に設定した作戦に基づいて行動します。</t>
   </si>
   <si>
-    <t>バトル結果</t>
+    <t>リザルト</t>
   </si>
   <si>
     <t>◇バトル勝敗
@@ -237,14 +237,14 @@
 属性適正値に応じて魔法習得する際の(Nu)使用量が変化します。
 また魔法のRankがRの場合は(Nu)使用量が2倍になります。
 ◇魔法について
-■種別
+■魔法種別
 魔法にはそれぞれ種別があります。
 ・Active
 バトルでターンがまわってきた際に使用します。
 基本的に同じターン内で発動する魔法の起点になります。
 ・Passive
 (条件)を満たしたとき自動で発動します。
-・Messiah
+Unique
 Passiveと同じく(条件)を満たしたとき自動で発動しさらに覚醒状態になります。
 バトル中1回だけ発動します。
 ・Awaken
@@ -352,10 +352,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -367,12 +367,81 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -381,9 +450,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -395,18 +487,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -424,91 +509,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -519,31 +519,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,151 +681,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,6 +710,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -730,6 +760,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -742,8 +781,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -771,45 +810,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -818,145 +818,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -171,7 +171,8 @@
 ◇バトルシステム
 ■バトル
 バトルは全てオートで進行します。
-キャラクターはそれぞれキャラ毎に設定した作戦に基づいて行動します。
+キャラクターはそれぞれキャラ毎に設定した作戦と
+バトル中に設定した優先対象に基づいて行動します。
 ◇バトル勝敗
 ■勝利時
 バトルの内容に応じてバトル評価を入手します。
@@ -200,7 +201,8 @@
     <t>◇バトルシステム
 ■バトル
 バトルは全てオートで進行します。
-キャラクターはそれぞれキャラ毎に設定した作戦に基づいて行動します。</t>
+キャラクターはそれぞれキャラ毎に設定した作戦と
+バトル中に設定した優先対象に基づいて行動します。</t>
   </si>
   <si>
     <t>リザルト</t>
@@ -237,14 +239,14 @@
 属性適正値に応じて魔法習得する際の(Nu)使用量が変化します。
 また魔法のRankがRの場合は(Nu)使用量が2倍になります。
 ◇魔法について
-■魔法種別
+■種別
 魔法にはそれぞれ種別があります。
 ・Active
 バトルでターンがまわってきた際に使用します。
 基本的に同じターン内で発動する魔法の起点になります。
 ・Passive
 (条件)を満たしたとき自動で発動します。
-Unique
+・Messiah
 Passiveと同じく(条件)を満たしたとき自動で発動しさらに覚醒状態になります。
 バトル中1回だけ発動します。
 ・Awaken
@@ -262,7 +264,14 @@
 Range.Lの魔法は配置にかかわらず対象にできます。
 ■CT
 一部の魔法にはCT(カウントターン)があります。
-CTは魔法を使用した後、再度使用できるまでの猶予ターンです。</t>
+CTは魔法を使用した後、再度使用できるまでの猶予ターンです。
+■作戦設定
+キャラクター毎にバトル中の行動を設定します。
+作戦は魔法毎に優先順位と2つまで条件を設定できます。
+キャラクターは優先順位の高い方から使用可能になった魔法を選択します。
+Acitve・Awaken魔法は作戦に設定しなければ使用しません。
+Passive・Unique魔法は作戦に設定しなくても発動しますが
+条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
   </si>
   <si>
     <t>パラメータ</t>
@@ -317,6 +326,18 @@
 CTは魔法を使用した後、再度使用できるまでの猶予ターンです。</t>
   </si>
   <si>
+    <t>作戦設定</t>
+  </si>
+  <si>
+    <t>■作戦設定
+キャラクター毎にバトル中の行動を設定します。
+作戦は魔法毎に優先順位と2つまで条件を設定できます。
+キャラクターは優先順位の高い方から使用可能になった魔法を選択します。
+Acitve・Awaken魔法は作戦に設定しなければ使用しません。
+Passive・Unique魔法は作戦に設定しなくても発動しますが
+条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
+  </si>
+  <si>
     <t>レベルアップ</t>
   </si>
   <si>
@@ -353,8 +374,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -366,10 +387,123 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -381,13 +515,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -396,66 +523,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -463,52 +530,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -519,187 +540,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,6 +731,65 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -743,65 +823,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -818,16 +839,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -836,127 +857,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1286,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.6363636363636" customWidth="1"/>
@@ -1499,86 +1520,103 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>10120</v>
+        <v>3030</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>1020</v>
+        <v>3000</v>
       </c>
       <c r="E13">
-        <v>1020</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E14">
-        <v>1030</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>10140</v>
+        <v>10130</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="E15">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>10150</v>
+        <v>10140</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="E16">
-        <v>1050</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>10160</v>
+        <v>10150</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17">
+        <v>1050</v>
+      </c>
+      <c r="E17">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>10160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18">
         <v>1060</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>1060</v>
       </c>
     </row>
@@ -1591,7 +1629,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1653,7 +1691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="286" spans="1:3">
+    <row r="6" ht="299" spans="1:3">
       <c r="A6">
         <v>2000</v>
       </c>
@@ -1675,7 +1713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="52" spans="1:3">
+    <row r="8" ht="65" spans="1:3">
       <c r="A8">
         <v>2020</v>
       </c>
@@ -1730,9 +1768,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="39" spans="1:3">
+    <row r="13" ht="117" spans="1:3">
       <c r="A13">
-        <v>10120</v>
+        <v>3030</v>
       </c>
       <c r="B13" t="s">
         <v>43</v>
@@ -1743,7 +1781,7 @@
     </row>
     <row r="14" ht="39" spans="1:3">
       <c r="A14">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
@@ -1754,7 +1792,7 @@
     </row>
     <row r="15" ht="39" spans="1:3">
       <c r="A15">
-        <v>10140</v>
+        <v>10130</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -1763,25 +1801,36 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" ht="39" spans="1:3">
       <c r="A16">
-        <v>10150</v>
+        <v>10140</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
-        <v>5</v>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
+        <v>10150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>10160</v>
       </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -167,7 +167,7 @@
 ■編成
 バトルに参加するメンバーは最大5名まで編成できます。
 メンバーはそれぞれ前列・後列に配置できます。
-Backに配置したメンバーはRangeがLの魔法のみ使用できます。
+Backに配置したメンバーはRangeがLargeの魔法のみ使用できます。
 ◇バトルシステム
 ■バトル
 バトルは全てオートで進行します。
@@ -259,9 +259,9 @@
 編成しているキャラクター全体に自動で効果が発動します。
 ■Range
 魔法にはそれぞれ攻撃範囲があります。
-Range.Sの魔法はBackに配置した敵を対象にできません。
+Range.Shortの魔法はBackに配置した敵を対象にできません。
 ただしFrontに配置した敵がいない場合は使用できます。
-Range.Lの魔法は配置にかかわらず対象にできます。
+Range.Largeの魔法は配置にかかわらず対象にできます。
 ■CT
 一部の魔法にはCT(カウントターン)があります。
 CTは魔法を使用した後、再度使用できるまでの猶予ターンです。
@@ -318,9 +318,9 @@
 編成しているキャラクター全体に自動で効果が発動します。
 ■Range
 魔法にはそれぞれ攻撃範囲があります。
-Range.Sの魔法はBackに配置した敵を対象にできません。
+Range.Shortの魔法はBackに配置した敵を対象にできません。
 ただしFrontに配置した敵がいない場合は使用できます。
-Range.Lの魔法は配置にかかわらず対象にできます。
+Range.Largeの魔法は配置にかかわらず対象にできます。
 ■CT
 一部の魔法にはCT(カウントターン)があります。
 CTは魔法を使用した後、再度使用できるまでの猶予ターンです。</t>
@@ -373,10 +373,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -384,6 +384,73 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -395,28 +462,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -424,22 +508,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,84 +530,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -540,187 +540,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -739,6 +739,45 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,50 +799,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -825,9 +823,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -839,145 +839,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
